--- a/templates/productie/productie_opdracht_template_full.xlsx
+++ b/templates/productie/productie_opdracht_template_full.xlsx
@@ -5714,13 +5714,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-03-31 16:51:21.094530</t>
+    <t>2026-05-06 16:21:20.332781</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.3.1</t>
   </si>
   <si>
     <t>xdov-version</t>

--- a/templates/productie/productie_opdracht_template_full.xlsx
+++ b/templates/productie/productie_opdracht_template_full.xlsx
@@ -5720,13 +5720,13 @@
     <t>Date generated</t>
   </si>
   <si>
-    <t>2026-05-19 11:28:52.446854</t>
+    <t>2026-05-19 14:52:44.751467</t>
   </si>
   <si>
     <t>version</t>
   </si>
   <si>
-    <t>2.4.0</t>
+    <t>2.4.1</t>
   </si>
   <si>
     <t>xdov-version</t>
